--- a/excel/14文本函数.xlsx
+++ b/excel/14文本函数.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10914"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Desktop/cli/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B5E476-DB3D-6C4F-8AB2-50849793C7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D069D0D3-40A2-654A-8093-88B95CC25B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3659" uniqueCount="3569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3674" uniqueCount="3584">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -10855,6 +10855,66 @@
   </si>
   <si>
     <t>取余函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以下函数都会返回的是文本类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文本数据在排序上比数值靠后 在判别文本是否大于数值都会返回真值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在Excel中数据可分为文本、数值、逻辑值、错误值等几种类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文本类型 带引号""或中文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值类型 负数、零和正数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻辑值 TRUE和FALSE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">错误值 #VALUE!、#DIV/0!、#NAME?、#N/A、#REF!、#NUM!和#NULL! </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>疑难杂题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数字与“空”相加得到#VALUE!错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用N(value)函数可以将文本转换为0、数值返回其本身的值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、数字与空单元格相加出错</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、空文本与空单元格的区别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文本在Excel中的表示方法是用一对半角双引号包含</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空文本是指双引号""中间什么内容也没有的文本 其字符长度为0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10862,7 +10922,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -10963,6 +11023,27 @@
     <font>
       <sz val="10"/>
       <color theme="3" tint="-0.249977111117893"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -11113,7 +11194,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -11184,22 +11265,13 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11211,13 +11283,31 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -11529,7 +11619,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor indexed="60"/>
   </sheetPr>
-  <dimension ref="A2:G61"/>
+  <dimension ref="A2:G70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -11550,330 +11640,403 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" ht="14"/>
+    <row r="5" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="B5" s="4"/>
+    </row>
     <row r="6" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C6" s="39" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="3" t="s">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="B7" s="4"/>
+      <c r="D7" s="3" t="s">
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="B8" s="4"/>
+      <c r="D8" s="3" t="s">
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="B9" s="4"/>
+      <c r="D9" s="3" t="s">
+        <v>3574</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="B10" s="4"/>
+      <c r="D10" s="3" t="s">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="B11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="B12" s="4"/>
+      <c r="C12" s="3" t="s">
+        <v>3569</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="B13" s="4"/>
+      <c r="C13" s="3" t="s">
+        <v>3570</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="3" customFormat="1" ht="14"/>
+    <row r="15" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="C15" s="28" t="s">
         <v>3536</v>
       </c>
-      <c r="D6" s="39"/>
-    </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C7" s="39" t="s">
+      <c r="D15" s="28"/>
+    </row>
+    <row r="16" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="C16" s="28" t="s">
         <v>3539</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D16" s="28" t="s">
         <v>3540</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C8" s="39" t="s">
+    <row r="17" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C17" s="28" t="s">
         <v>3541</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D17" s="28" t="s">
         <v>3542</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-    </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C10" s="39" t="s">
+    <row r="18" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+    </row>
+    <row r="19" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C19" s="28" t="s">
         <v>3537</v>
       </c>
-      <c r="D10" s="39"/>
-    </row>
-    <row r="11" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C11" s="39" t="s">
+      <c r="D19" s="28"/>
+    </row>
+    <row r="20" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C20" s="28" t="s">
         <v>3539</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D20" s="28" t="s">
         <v>3540</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C12" s="39" t="s">
+    <row r="21" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C21" s="28" t="s">
         <v>3541</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D21" s="28" t="s">
         <v>3542</v>
       </c>
     </row>
-    <row r="13" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-    </row>
-    <row r="14" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C14" s="39" t="s">
+    <row r="22" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+    </row>
+    <row r="23" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C23" s="28" t="s">
         <v>3538</v>
       </c>
-      <c r="D14" s="39"/>
-    </row>
-    <row r="15" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C15" s="39" t="s">
+      <c r="D23" s="28"/>
+    </row>
+    <row r="24" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C24" s="28" t="s">
         <v>3539</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D24" s="28" t="s">
         <v>3540</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C16" s="39" t="s">
+    <row r="25" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C25" s="28" t="s">
         <v>3541</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D25" s="28" t="s">
         <v>3543</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C17" s="39" t="s">
+    <row r="26" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C26" s="28" t="s">
         <v>3544</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D26" s="28" t="s">
         <v>3542</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C18" s="39" t="s">
+    <row r="27" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C27" s="28" t="s">
         <v>3545</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C19" s="39"/>
-    </row>
-    <row r="20" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C20" s="39" t="s">
+    <row r="28" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C28" s="28"/>
+    </row>
+    <row r="29" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C29" s="28" t="s">
         <v>3546</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C21" s="39" t="s">
+    <row r="30" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C30" s="28" t="s">
         <v>3539</v>
       </c>
-      <c r="D21" s="39" t="s">
+      <c r="D30" s="28" t="s">
         <v>3547</v>
       </c>
     </row>
-    <row r="22" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C22" s="39" t="s">
+    <row r="31" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C31" s="28" t="s">
         <v>3541</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="D31" s="28" t="s">
         <v>3548</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C23" s="39" t="s">
+    <row r="32" spans="3:4" s="3" customFormat="1" ht="14">
+      <c r="C32" s="28" t="s">
         <v>3544</v>
       </c>
-      <c r="D23" s="39" t="s">
+      <c r="D32" s="28" t="s">
         <v>3549</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-    </row>
-    <row r="25" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C25" s="39" t="s">
+    <row r="33" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+    </row>
+    <row r="34" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="C34" s="28" t="s">
         <v>3550</v>
       </c>
-      <c r="D25" s="39"/>
-    </row>
-    <row r="26" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C26" s="39" t="s">
+      <c r="D34" s="28"/>
+    </row>
+    <row r="35" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="C35" s="28" t="s">
         <v>3539</v>
       </c>
-      <c r="D26" s="39" t="s">
+      <c r="D35" s="28" t="s">
         <v>3540</v>
       </c>
     </row>
-    <row r="27" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C27" s="39" t="s">
+    <row r="36" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="C36" s="28" t="s">
         <v>3541</v>
       </c>
-      <c r="D27" s="39" t="s">
+      <c r="D36" s="28" t="s">
         <v>3551</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C28" s="39" t="s">
+    <row r="37" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="C37" s="28" t="s">
         <v>3544</v>
       </c>
-      <c r="D28" s="39" t="s">
+      <c r="D37" s="28" t="s">
         <v>3552</v>
       </c>
     </row>
-    <row r="29" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C29" s="39" t="s">
+    <row r="38" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="C38" s="28" t="s">
         <v>3553</v>
       </c>
-      <c r="D29" s="39" t="s">
+      <c r="D38" s="28" t="s">
         <v>3554</v>
       </c>
     </row>
-    <row r="30" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-    </row>
-    <row r="31" spans="1:4" s="3" customFormat="1" ht="14">
-      <c r="A31" s="3" t="s">
+    <row r="39" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+    </row>
+    <row r="40" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="A40" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B40" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:4" s="3" customFormat="1" ht="14"/>
-    <row r="33" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="B33" s="3" t="s">
+    <row r="41" spans="1:4" s="3" customFormat="1" ht="14"/>
+    <row r="42" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="B42" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="C34" s="39" t="s">
+    <row r="43" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="C43" s="28" t="s">
         <v>3555</v>
       </c>
-      <c r="D34" s="39" t="s">
+      <c r="D43" s="28" t="s">
         <v>3556</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="C35" s="39" t="s">
+    <row r="44" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="C44" s="28" t="s">
         <v>3557</v>
       </c>
-      <c r="D35" s="39" t="s">
+      <c r="D44" s="28" t="s">
         <v>3558</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="C36" s="39" t="s">
+    <row r="45" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="C45" s="28" t="s">
         <v>3563</v>
       </c>
-      <c r="D36" s="39"/>
-    </row>
-    <row r="37" spans="1:7" s="3" customFormat="1" ht="14"/>
-    <row r="38" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="B38" s="3" t="s">
+      <c r="D45" s="28"/>
+    </row>
+    <row r="46" spans="1:4" s="3" customFormat="1" ht="14"/>
+    <row r="47" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="B47" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="C39" s="39" t="s">
+    <row r="48" spans="1:4" s="3" customFormat="1" ht="14">
+      <c r="C48" s="28" t="s">
         <v>3560</v>
       </c>
-      <c r="D39" s="39"/>
-    </row>
-    <row r="40" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="C40" s="39" t="s">
+      <c r="D48" s="28"/>
+    </row>
+    <row r="49" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="C49" s="28" t="s">
         <v>3559</v>
       </c>
-      <c r="D40" s="39"/>
-    </row>
-    <row r="41" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="C41" s="39" t="s">
+      <c r="D49" s="28"/>
+    </row>
+    <row r="50" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="C50" s="28" t="s">
         <v>3539</v>
       </c>
-      <c r="D41" s="39" t="s">
+      <c r="D50" s="28" t="s">
         <v>3561</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="3" customFormat="1">
-      <c r="C42" s="39" t="s">
+    <row r="51" spans="1:7" s="3" customFormat="1">
+      <c r="C51" s="28" t="s">
         <v>3541</v>
       </c>
-      <c r="D42" s="39" t="s">
+      <c r="D51" s="28" t="s">
         <v>3540</v>
       </c>
-      <c r="G42" s="6"/>
-    </row>
-    <row r="43" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="C43" s="39" t="s">
+      <c r="G51" s="6"/>
+    </row>
+    <row r="52" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="C52" s="28" t="s">
         <v>3544</v>
       </c>
-      <c r="D43" s="39" t="s">
+      <c r="D52" s="28" t="s">
         <v>3562</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="3" customFormat="1" ht="14"/>
-    <row r="45" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="A45" s="3" t="s">
+    <row r="53" spans="1:7" s="3" customFormat="1" ht="14"/>
+    <row r="54" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="A54" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B54" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="3" customFormat="1" ht="14"/>
-    <row r="47" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="B47" s="39" t="s">
+    <row r="55" spans="1:7" s="3" customFormat="1" ht="14"/>
+    <row r="56" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="B56" s="28" t="s">
         <v>3564</v>
       </c>
-      <c r="C47" s="39" t="s">
+      <c r="C56" s="28" t="s">
         <v>3565</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="B48" s="39" t="s">
+    <row r="57" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="B57" s="28" t="s">
         <v>3568</v>
       </c>
-      <c r="C48" s="39" t="s">
+      <c r="C57" s="28" t="s">
         <v>3539</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>3566</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="B49" s="39"/>
-      <c r="C49" s="39" t="s">
+    <row r="58" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="B58" s="28"/>
+      <c r="C58" s="28" t="s">
         <v>3541</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>3567</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="B50" s="39" t="s">
+    <row r="59" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="B59" s="28" t="s">
         <v>3519</v>
       </c>
-      <c r="C50" s="39"/>
-    </row>
-    <row r="51" spans="1:7" s="3" customFormat="1" ht="14"/>
-    <row r="52" spans="1:7" s="3" customFormat="1" ht="14"/>
-    <row r="53" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="C53" s="5"/>
-    </row>
-    <row r="54" spans="1:7" s="3" customFormat="1" ht="14">
-      <c r="C54" s="5"/>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="C56" s="3"/>
-      <c r="E56" s="3"/>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="C57" s="3"/>
-      <c r="E57" s="3"/>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="E58" s="3"/>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="E59" s="3"/>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="E60" s="3"/>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="E61" s="3"/>
+      <c r="C59" s="28"/>
+    </row>
+    <row r="60" spans="1:7" s="3" customFormat="1" ht="14"/>
+    <row r="61" spans="1:7" s="3" customFormat="1" ht="14"/>
+    <row r="62" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="A62" s="3" t="s">
+        <v>3576</v>
+      </c>
+      <c r="B62" s="40" t="s">
+        <v>3577</v>
+      </c>
+      <c r="C62" s="5"/>
+    </row>
+    <row r="63" spans="1:7" s="3" customFormat="1" ht="14">
+      <c r="C63" s="5"/>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="3"/>
+      <c r="B64" s="42" t="s">
+        <v>3580</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+    </row>
+    <row r="65" spans="2:5">
+      <c r="C65" s="41" t="s">
+        <v>3578</v>
+      </c>
+      <c r="E65" s="3"/>
+    </row>
+    <row r="66" spans="2:5">
+      <c r="C66" s="41" t="s">
+        <v>3579</v>
+      </c>
+      <c r="E66" s="3"/>
+    </row>
+    <row r="67" spans="2:5">
+      <c r="B67" s="41"/>
+      <c r="E67" s="3"/>
+    </row>
+    <row r="68" spans="2:5">
+      <c r="B68" s="3" t="s">
+        <v>3581</v>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="E68" s="3"/>
+    </row>
+    <row r="69" spans="2:5">
+      <c r="B69" s="3"/>
+      <c r="C69" s="41" t="s">
+        <v>3582</v>
+      </c>
+      <c r="E69" s="3"/>
+    </row>
+    <row r="70" spans="2:5">
+      <c r="C70" s="41" t="s">
+        <v>3583</v>
+      </c>
+      <c r="E70" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12668,22 +12831,22 @@
         <v>6</v>
       </c>
       <c r="D1" s="7"/>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="F1" s="30"/>
+      <c r="G1" s="30" t="s">
         <v>3520</v>
       </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28" t="s">
+      <c r="H1" s="30"/>
+      <c r="I1" s="30" t="s">
         <v>3521</v>
       </c>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28" t="s">
+      <c r="J1" s="30"/>
+      <c r="K1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="28"/>
+      <c r="L1" s="30"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="17" t="s">
@@ -12698,25 +12861,25 @@
         <v>文泰来</v>
       </c>
       <c r="D2" s="7"/>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="34"/>
-      <c r="G2" s="35" t="str">
+      <c r="F2" s="31"/>
+      <c r="G2" s="32" t="str">
         <f>LEFT(RIGHT(E2,7),3)</f>
         <v>313</v>
       </c>
-      <c r="H2" s="36"/>
-      <c r="I2" s="35" t="str">
+      <c r="H2" s="33"/>
+      <c r="I2" s="32" t="str">
         <f>MID(E2,3,3)</f>
         <v>313</v>
       </c>
-      <c r="J2" s="36"/>
-      <c r="K2" s="34" t="str">
+      <c r="J2" s="33"/>
+      <c r="K2" s="31" t="str">
         <f>RIGHT(E2,4)</f>
         <v>7200</v>
       </c>
-      <c r="L2" s="34"/>
+      <c r="L2" s="31"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1">
       <c r="A3" s="16" t="s">
@@ -12731,25 +12894,25 @@
         <v>徐天宏</v>
       </c>
       <c r="D3" s="7"/>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="31"/>
-      <c r="G3" s="32" t="str">
+      <c r="F3" s="29"/>
+      <c r="G3" s="34" t="str">
         <f t="shared" ref="G3:G5" si="2">LEFT(RIGHT(E3,7),3)</f>
         <v>308</v>
       </c>
-      <c r="H3" s="33"/>
-      <c r="I3" s="32" t="str">
+      <c r="H3" s="35"/>
+      <c r="I3" s="34" t="str">
         <f t="shared" ref="I3:I5" si="3">MID(E3,3,3)</f>
         <v>308</v>
       </c>
-      <c r="J3" s="33"/>
-      <c r="K3" s="31" t="str">
+      <c r="J3" s="35"/>
+      <c r="K3" s="29" t="str">
         <f t="shared" ref="K3:K5" si="4">RIGHT(E3,4)</f>
         <v>1980</v>
       </c>
-      <c r="L3" s="31"/>
+      <c r="L3" s="29"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1">
       <c r="A4" s="16" t="s">
@@ -12764,25 +12927,25 @@
         <v>骆冰</v>
       </c>
       <c r="D4" s="7"/>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="31"/>
-      <c r="G4" s="32" t="str">
+      <c r="F4" s="29"/>
+      <c r="G4" s="34" t="str">
         <f t="shared" si="2"/>
         <v>330</v>
       </c>
-      <c r="H4" s="33"/>
-      <c r="I4" s="32" t="str">
+      <c r="H4" s="35"/>
+      <c r="I4" s="34" t="str">
         <f t="shared" si="3"/>
         <v>330</v>
       </c>
-      <c r="J4" s="33"/>
-      <c r="K4" s="31" t="str">
+      <c r="J4" s="35"/>
+      <c r="K4" s="29" t="str">
         <f t="shared" si="4"/>
         <v>3088</v>
       </c>
-      <c r="L4" s="31"/>
+      <c r="L4" s="29"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1">
       <c r="A5" s="16" t="s">
@@ -12797,25 +12960,25 @@
         <v>石双英</v>
       </c>
       <c r="D5" s="7"/>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="31"/>
-      <c r="G5" s="32" t="str">
+      <c r="F5" s="29"/>
+      <c r="G5" s="34" t="str">
         <f t="shared" si="2"/>
         <v>284</v>
       </c>
-      <c r="H5" s="33"/>
-      <c r="I5" s="32" t="str">
+      <c r="H5" s="35"/>
+      <c r="I5" s="34" t="str">
         <f t="shared" si="3"/>
         <v>284</v>
       </c>
-      <c r="J5" s="33"/>
-      <c r="K5" s="31" t="str">
+      <c r="J5" s="35"/>
+      <c r="K5" s="29" t="str">
         <f t="shared" si="4"/>
         <v>7219</v>
       </c>
-      <c r="L5" s="31"/>
+      <c r="L5" s="29"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1">
       <c r="F9" s="15" t="s">
@@ -12841,10 +13004,10 @@
       <c r="A10" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="28"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="19" t="s">
         <v>26</v>
       </c>
@@ -12872,10 +13035,10 @@
       <c r="A11" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="29"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="17" t="str">
         <f>RIGHT(LEFT(B11,17),1)</f>
         <v>1</v>
@@ -12904,10 +13067,10 @@
       <c r="A12" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="30"/>
+      <c r="C12" s="37"/>
       <c r="D12" s="16" t="str">
         <f t="shared" ref="D12:D14" si="6">RIGHT(LEFT(B12,17),1)</f>
         <v>3</v>
@@ -12936,10 +13099,10 @@
       <c r="A13" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="30"/>
+      <c r="C13" s="37"/>
       <c r="D13" s="16" t="str">
         <f t="shared" si="6"/>
         <v>2</v>
@@ -12968,10 +13131,10 @@
       <c r="A14" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="30"/>
+      <c r="C14" s="37"/>
       <c r="D14" s="16" t="str">
         <f t="shared" si="6"/>
         <v>1</v>
@@ -13291,6 +13454,19 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I5:J5"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="E1:F1"/>
@@ -13303,19 +13479,6 @@
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="I3:J3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13332,19 +13495,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="30" t="s">
         <v>30</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="28"/>
+      <c r="G1" s="30"/>
       <c r="H1" s="19" t="s">
         <v>32</v>
       </c>
@@ -13353,18 +13516,18 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="36" t="s">
         <v>3514</v>
       </c>
-      <c r="B2" s="29"/>
+      <c r="B2" s="36"/>
       <c r="C2" s="17" t="str">
         <f>RIGHT(A2,LENB(A2)-LEN(A2))</f>
         <v>元</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="29"/>
+      <c r="G2" s="36"/>
       <c r="H2" s="17" t="str">
         <f>LEFT(F2,FIND("@",F2)-1)</f>
         <v>zhangsan</v>
@@ -13375,18 +13538,18 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="37" t="s">
         <v>3515</v>
       </c>
-      <c r="B3" s="30"/>
+      <c r="B3" s="37"/>
       <c r="C3" s="16" t="str">
         <f t="shared" ref="C3:C9" si="0">RIGHT(A3,LENB(A3)-LEN(A3))</f>
         <v>千克</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="30"/>
+      <c r="G3" s="37"/>
       <c r="H3" s="16" t="str">
         <f t="shared" ref="H3:H4" si="1">LEFT(F3,FIND("@",F3)-1)</f>
         <v>lisi</v>
@@ -13397,18 +13560,18 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="30"/>
+      <c r="B4" s="37"/>
       <c r="C4" s="16" t="str">
         <f t="shared" si="0"/>
         <v>克</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="30"/>
+      <c r="G4" s="37"/>
       <c r="H4" s="16" t="str">
         <f t="shared" si="1"/>
         <v>wangwu</v>
@@ -13419,50 +13582,50 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="30"/>
+      <c r="B5" s="37"/>
       <c r="C5" s="16" t="str">
         <f t="shared" si="0"/>
         <v>公斤</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="30"/>
+      <c r="B6" s="37"/>
       <c r="C6" s="16" t="str">
         <f t="shared" si="0"/>
         <v>人次</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="30"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="16" t="str">
         <f t="shared" si="0"/>
         <v>个</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="30"/>
+      <c r="B8" s="37"/>
       <c r="C8" s="16" t="str">
         <f t="shared" si="0"/>
         <v>将</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="30"/>
+      <c r="B9" s="37"/>
       <c r="C9" s="16" t="str">
         <f t="shared" si="0"/>
         <v>摄氏度</v>
@@ -13470,6 +13633,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="F3:G3"/>
@@ -13478,11 +13646,6 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13506,10 +13669,10 @@
       <c r="A1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="28"/>
+      <c r="C1" s="30"/>
       <c r="D1" s="27" t="s">
         <v>3509</v>
       </c>
@@ -13527,10 +13690,10 @@
       <c r="A2" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="38" t="s">
         <v>3522</v>
       </c>
-      <c r="C2" s="37"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="24" t="str">
         <f>VLOOKUP(--LEFT(B2,6),地区码!A:B,2,0)</f>
         <v>北京市朝阳区</v>
@@ -13552,10 +13715,10 @@
       <c r="A3" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="39" t="s">
         <v>3523</v>
       </c>
-      <c r="C3" s="38"/>
+      <c r="C3" s="39"/>
       <c r="D3" s="21" t="str">
         <f>VLOOKUP(--LEFT(B3,6),地区码!A:B,2,0)</f>
         <v>四川省自贡市</v>
